--- a/Remise.xlsx
+++ b/Remise.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77C018A9-4A7E-46A9-B6B4-3652361B40FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DEB1F74-B94E-4CAB-A216-D8E22A280F9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15" yWindow="15" windowWidth="19185" windowHeight="10785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Date</t>
   </si>
@@ -54,6 +54,9 @@
   </si>
   <si>
     <t>Ngouye NDIAYE</t>
+  </si>
+  <si>
+    <t>Ndack NDAO</t>
   </si>
 </sst>
 </file>
@@ -139,6 +142,7 @@
         <name val="TIMES"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
     </dxf>
     <dxf>
       <font>
@@ -156,7 +160,6 @@
         <name val="TIMES"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
     </dxf>
     <dxf>
       <font>
@@ -241,14 +244,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B22887BA-DDF2-48BF-9437-28C91CB5F792}" name="Tableau1" displayName="Tableau1" ref="A1:E2" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
-  <autoFilter ref="A1:E2" xr:uid="{B22887BA-DDF2-48BF-9437-28C91CB5F792}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B22887BA-DDF2-48BF-9437-28C91CB5F792}" name="Tableau1" displayName="Tableau1" ref="A1:E3" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+  <autoFilter ref="A1:E3" xr:uid="{B22887BA-DDF2-48BF-9437-28C91CB5F792}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{1100C874-2ACC-444F-9559-0BA97B2B95C4}" name="Date" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{60CF5FB0-B425-43F1-A81D-1D127E0F488D}" name="Equipe" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{1DC21C64-05F3-47E6-81D1-13FAC1E2457E}" name="Agent" dataDxfId="0"/>
-    <tableColumn id="3" xr3:uid="{B3D7358F-00E0-45C2-8B00-3057DAFF7F96}" name="Montant" dataDxfId="2"/>
-    <tableColumn id="16" xr3:uid="{1D80340E-085A-4C8C-AC9C-85DF95DFF70B}" name="Numero_semaine" dataDxfId="1">
+    <tableColumn id="4" xr3:uid="{1DC21C64-05F3-47E6-81D1-13FAC1E2457E}" name="Agent" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{B3D7358F-00E0-45C2-8B00-3057DAFF7F96}" name="Montant" dataDxfId="1"/>
+    <tableColumn id="16" xr3:uid="{1D80340E-085A-4C8C-AC9C-85DF95DFF70B}" name="Numero_semaine" dataDxfId="0">
       <calculatedColumnFormula>"S"&amp;_xlfn.ISOWEEKNUM(Tableau1[[#This Row],[Date]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -618,11 +621,20 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A3" s="2"/>
+      <c r="A3" s="2">
+        <v>46198</v>
+      </c>
       <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
+      <c r="C3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="3">
+        <v>50000</v>
+      </c>
+      <c r="E3" s="1" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Tableau1[[#This Row],[Date]])</f>
+        <v>S26</v>
+      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" s="2"/>

--- a/Remise.xlsx
+++ b/Remise.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DEB1F74-B94E-4CAB-A216-D8E22A280F9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B321E7F-7A8A-4433-B28C-F4FEB8937AC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15" yWindow="15" windowWidth="19185" windowHeight="10785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Date</t>
   </si>
@@ -57,6 +57,9 @@
   </si>
   <si>
     <t>Ndack NDAO</t>
+  </si>
+  <si>
+    <t>AMINATA NDIAYE</t>
   </si>
 </sst>
 </file>
@@ -244,8 +247,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B22887BA-DDF2-48BF-9437-28C91CB5F792}" name="Tableau1" displayName="Tableau1" ref="A1:E3" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
-  <autoFilter ref="A1:E3" xr:uid="{B22887BA-DDF2-48BF-9437-28C91CB5F792}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B22887BA-DDF2-48BF-9437-28C91CB5F792}" name="Tableau1" displayName="Tableau1" ref="A1:E4" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+  <autoFilter ref="A1:E4" xr:uid="{B22887BA-DDF2-48BF-9437-28C91CB5F792}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{1100C874-2ACC-444F-9559-0BA97B2B95C4}" name="Date" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{60CF5FB0-B425-43F1-A81D-1D127E0F488D}" name="Equipe" dataDxfId="3"/>
@@ -637,11 +640,20 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A4" s="2"/>
+      <c r="A4" s="2">
+        <v>46198</v>
+      </c>
       <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
+      <c r="C4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E4" s="1" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Tableau1[[#This Row],[Date]])</f>
+        <v>S26</v>
+      </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" s="2"/>

--- a/Remise.xlsx
+++ b/Remise.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B321E7F-7A8A-4433-B28C-F4FEB8937AC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A384AFB-DC52-4274-9A0A-665389E42C43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15" yWindow="15" windowWidth="19185" windowHeight="10785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>Date</t>
   </si>
@@ -60,6 +60,12 @@
   </si>
   <si>
     <t>AMINATA NDIAYE</t>
+  </si>
+  <si>
+    <t>TOUBA</t>
+  </si>
+  <si>
+    <t>TATA 1</t>
   </si>
 </sst>
 </file>
@@ -247,8 +253,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B22887BA-DDF2-48BF-9437-28C91CB5F792}" name="Tableau1" displayName="Tableau1" ref="A1:E4" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
-  <autoFilter ref="A1:E4" xr:uid="{B22887BA-DDF2-48BF-9437-28C91CB5F792}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B22887BA-DDF2-48BF-9437-28C91CB5F792}" name="Tableau1" displayName="Tableau1" ref="A1:E5" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+  <autoFilter ref="A1:E5" xr:uid="{B22887BA-DDF2-48BF-9437-28C91CB5F792}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{1100C874-2ACC-444F-9559-0BA97B2B95C4}" name="Date" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{60CF5FB0-B425-43F1-A81D-1D127E0F488D}" name="Equipe" dataDxfId="3"/>
@@ -656,11 +662,22 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A5" s="2"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
+      <c r="A5" s="2">
+        <v>46233</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="3">
+        <v>731800</v>
+      </c>
+      <c r="E5" s="1" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Tableau1[[#This Row],[Date]])</f>
+        <v>S31</v>
+      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" s="2"/>

--- a/Remise.xlsx
+++ b/Remise.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A384AFB-DC52-4274-9A0A-665389E42C43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36C0D763-D9F5-4494-8CB6-B8AE40B41954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
   <si>
     <t>Date</t>
   </si>
@@ -65,7 +65,10 @@
     <t>TOUBA</t>
   </si>
   <si>
-    <t>TATA 1</t>
+    <t>evapore</t>
+  </si>
+  <si>
+    <t>cowmilk 200g</t>
   </si>
 </sst>
 </file>
@@ -253,8 +256,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B22887BA-DDF2-48BF-9437-28C91CB5F792}" name="Tableau1" displayName="Tableau1" ref="A1:E5" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
-  <autoFilter ref="A1:E5" xr:uid="{B22887BA-DDF2-48BF-9437-28C91CB5F792}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B22887BA-DDF2-48BF-9437-28C91CB5F792}" name="Tableau1" displayName="Tableau1" ref="A1:E6" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+  <autoFilter ref="A1:E6" xr:uid="{B22887BA-DDF2-48BF-9437-28C91CB5F792}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{1100C874-2ACC-444F-9559-0BA97B2B95C4}" name="Date" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{60CF5FB0-B425-43F1-A81D-1D127E0F488D}" name="Equipe" dataDxfId="3"/>
@@ -585,7 +588,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E8520"/>
+  <dimension ref="A1:I8520"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12.3984375" customWidth="1"/>
@@ -594,7 +597,7 @@
     <col min="5" max="5" width="17.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -611,7 +614,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="2">
         <v>46155</v>
       </c>
@@ -629,7 +632,7 @@
         <v>S20</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="2">
         <v>46198</v>
       </c>
@@ -644,8 +647,12 @@
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Tableau1[[#This Row],[Date]])</f>
         <v>S26</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="I3">
+        <f>69.7*750</f>
+        <v>52275</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" s="2">
         <v>46198</v>
       </c>
@@ -661,7 +668,7 @@
         <v>S26</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" s="2">
         <v>46233</v>
       </c>
@@ -672,84 +679,95 @@
         <v>10</v>
       </c>
       <c r="D5" s="3">
-        <v>731800</v>
+        <v>100000</v>
       </c>
       <c r="E5" s="1" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Tableau1[[#This Row],[Date]])</f>
         <v>S31</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A6" s="2"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A6" s="2">
+        <v>46233</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="3">
+        <v>52275</v>
+      </c>
+      <c r="E6" s="1" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Tableau1[[#This Row],[Date]])</f>
+        <v>S31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" s="2"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" s="2"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9" s="2"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" s="2"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11" s="2"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A12" s="2"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A13" s="2"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A14" s="2"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A15" s="2"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A16" s="2"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>

--- a/Remise.xlsx
+++ b/Remise.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36C0D763-D9F5-4494-8CB6-B8AE40B41954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D34D1CA3-B0E0-49FF-A350-96EAE126C6EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -65,10 +65,10 @@
     <t>TOUBA</t>
   </si>
   <si>
-    <t>evapore</t>
+    <t>cowmilk 200g (7*750 )</t>
   </si>
   <si>
-    <t>cowmilk 200g</t>
+    <t>cowmilk 5g (100*1000)</t>
   </si>
 </sst>
 </file>
@@ -111,11 +111,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -588,16 +589,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I8520"/>
+  <dimension ref="A1:J8520"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12.3984375" customWidth="1"/>
     <col min="2" max="3" width="25" customWidth="1"/>
     <col min="4" max="4" width="8.59765625" customWidth="1"/>
     <col min="5" max="5" width="17.796875" customWidth="1"/>
+    <col min="11" max="11" width="10.86328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -614,7 +616,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2" s="2">
         <v>46155</v>
       </c>
@@ -632,7 +634,7 @@
         <v>S20</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3" s="2">
         <v>46198</v>
       </c>
@@ -647,12 +649,10 @@
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Tableau1[[#This Row],[Date]])</f>
         <v>S26</v>
       </c>
-      <c r="I3">
-        <f>69.7*750</f>
-        <v>52275</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A4" s="2">
         <v>46198</v>
       </c>
@@ -667,8 +667,10 @@
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Tableau1[[#This Row],[Date]])</f>
         <v>S26</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A5" s="2">
         <v>46233</v>
       </c>
@@ -676,7 +678,7 @@
         <v>9</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" s="3">
         <v>100000</v>
@@ -685,8 +687,10 @@
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Tableau1[[#This Row],[Date]])</f>
         <v>S31</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A6" s="2">
         <v>46233</v>
       </c>
@@ -694,80 +698,86 @@
         <v>9</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D6" s="3">
-        <v>52275</v>
+        <v>5250</v>
       </c>
       <c r="E6" s="1" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Tableau1[[#This Row],[Date]])</f>
         <v>S31</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A7" s="2"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A8" s="2"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A9" s="2"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A10" s="2"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A11" s="2"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A12" s="2"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A13" s="2"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A14" s="2"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A15" s="2"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A16" s="2"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>

--- a/Remise.xlsx
+++ b/Remise.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D34D1CA3-B0E0-49FF-A350-96EAE126C6EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0A2980C-E4CB-4964-85CB-7BCEB80D2BCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
   <si>
     <t>Date</t>
   </si>
@@ -69,6 +69,9 @@
   </si>
   <si>
     <t>cowmilk 5g (100*1000)</t>
+  </si>
+  <si>
+    <t>INCONNUE</t>
   </si>
 </sst>
 </file>
@@ -257,8 +260,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B22887BA-DDF2-48BF-9437-28C91CB5F792}" name="Tableau1" displayName="Tableau1" ref="A1:E6" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
-  <autoFilter ref="A1:E6" xr:uid="{B22887BA-DDF2-48BF-9437-28C91CB5F792}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B22887BA-DDF2-48BF-9437-28C91CB5F792}" name="Tableau1" displayName="Tableau1" ref="A1:E7" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+  <autoFilter ref="A1:E7" xr:uid="{B22887BA-DDF2-48BF-9437-28C91CB5F792}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{1100C874-2ACC-444F-9559-0BA97B2B95C4}" name="Date" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{60CF5FB0-B425-43F1-A81D-1D127E0F488D}" name="Equipe" dataDxfId="3"/>
@@ -711,11 +714,22 @@
       <c r="J6" s="4"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A7" s="2"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
+      <c r="A7" s="2">
+        <v>46233</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="3">
+        <v>453226</v>
+      </c>
+      <c r="E7" s="1" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Tableau1[[#This Row],[Date]])</f>
+        <v>S31</v>
+      </c>
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
     </row>

--- a/Remise.xlsx
+++ b/Remise.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0A2980C-E4CB-4964-85CB-7BCEB80D2BCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{339B1B37-7160-47DF-A9DE-39ADDEEABB9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="15">
   <si>
     <t>Date</t>
   </si>
@@ -72,6 +72,12 @@
   </si>
   <si>
     <t>INCONNUE</t>
+  </si>
+  <si>
+    <t>NDACKNDAO  0005904</t>
+  </si>
+  <si>
+    <t>FATOUMA TRAORE (Thé 7g : 0005916</t>
   </si>
 </sst>
 </file>
@@ -260,8 +266,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B22887BA-DDF2-48BF-9437-28C91CB5F792}" name="Tableau1" displayName="Tableau1" ref="A1:E7" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
-  <autoFilter ref="A1:E7" xr:uid="{B22887BA-DDF2-48BF-9437-28C91CB5F792}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B22887BA-DDF2-48BF-9437-28C91CB5F792}" name="Tableau1" displayName="Tableau1" ref="A1:E9" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+  <autoFilter ref="A1:E9" xr:uid="{B22887BA-DDF2-48BF-9437-28C91CB5F792}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{1100C874-2ACC-444F-9559-0BA97B2B95C4}" name="Date" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{60CF5FB0-B425-43F1-A81D-1D127E0F488D}" name="Equipe" dataDxfId="3"/>
@@ -592,11 +598,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J8520"/>
+  <dimension ref="A1:J8522"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12.3984375" customWidth="1"/>
-    <col min="2" max="3" width="25" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="3" max="3" width="33.19921875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.59765625" customWidth="1"/>
     <col min="5" max="5" width="17.796875" customWidth="1"/>
     <col min="11" max="11" width="10.86328125" customWidth="1"/>
@@ -734,20 +741,42 @@
       <c r="J7" s="4"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A8" s="2"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
+      <c r="A8" s="2">
+        <v>46256</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E8" s="1" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Tableau1[[#This Row],[Date]])</f>
+        <v>S34</v>
+      </c>
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A9" s="2"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
+      <c r="A9" s="2">
+        <v>46256</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="3">
+        <v>16750</v>
+      </c>
+      <c r="E9" s="1" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Tableau1[[#This Row],[Date]])</f>
+        <v>S34</v>
+      </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A10" s="2"/>
@@ -60325,6 +60354,20 @@
       <c r="C8520" s="1"/>
       <c r="D8520" s="1"/>
       <c r="E8520" s="1"/>
+    </row>
+    <row r="8521" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A8521" s="2"/>
+      <c r="B8521" s="1"/>
+      <c r="C8521" s="1"/>
+      <c r="D8521" s="1"/>
+      <c r="E8521" s="1"/>
+    </row>
+    <row r="8522" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A8522" s="2"/>
+      <c r="B8522" s="1"/>
+      <c r="C8522" s="1"/>
+      <c r="D8522" s="1"/>
+      <c r="E8522" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
